--- a/docs/Mapping_casi_uso/matrimoni/Matr_008.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_008.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3276" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3269" uniqueCount="313">
   <si>
     <t>Sezione</t>
   </si>
@@ -255,12 +255,6 @@
   </si>
   <si>
     <t>minutoEvento</t>
-  </si>
-  <si>
-    <t>Presentazione documenti</t>
-  </si>
-  <si>
-    <t>datiProdotti</t>
   </si>
   <si>
     <t>Dichiarante</t>
@@ -1015,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H468"/>
+  <dimension ref="A1:H467"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.65625" customWidth="true" bestFit="true"/>
@@ -2096,7 +2090,7 @@
         <v>52</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>82</v>
@@ -2156,10 +2150,10 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>52</v>
@@ -2168,7 +2162,7 @@
         <v>75</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
@@ -2179,7 +2173,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>90</v>
@@ -2188,10 +2182,10 @@
         <v>52</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
@@ -2202,16 +2196,16 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>94</v>
@@ -2225,16 +2219,16 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>96</v>
@@ -2248,7 +2242,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>97</v>
@@ -2257,7 +2251,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>98</v>
@@ -2271,7 +2265,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>99</v>
@@ -2280,7 +2274,7 @@
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>100</v>
@@ -2294,7 +2288,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>101</v>
@@ -2303,7 +2297,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>102</v>
@@ -2317,7 +2311,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>103</v>
@@ -2326,7 +2320,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>104</v>
@@ -2340,7 +2334,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>105</v>
@@ -2349,7 +2343,7 @@
         <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>106</v>
@@ -2363,7 +2357,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>107</v>
@@ -2372,7 +2366,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>108</v>
@@ -2386,7 +2380,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>109</v>
@@ -2395,7 +2389,7 @@
         <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>110</v>
@@ -2409,7 +2403,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>111</v>
@@ -2418,7 +2412,7 @@
         <v>9</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>112</v>
@@ -2432,7 +2426,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>113</v>
@@ -2441,7 +2435,7 @@
         <v>9</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>114</v>
@@ -2455,7 +2449,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>115</v>
@@ -2464,7 +2458,7 @@
         <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>116</v>
@@ -2478,7 +2472,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>117</v>
@@ -2487,7 +2481,7 @@
         <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>118</v>
@@ -2501,7 +2495,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>119</v>
@@ -2510,7 +2504,7 @@
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>120</v>
@@ -2524,7 +2518,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>121</v>
@@ -2533,7 +2527,7 @@
         <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>122</v>
@@ -2547,7 +2541,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>123</v>
@@ -2556,7 +2550,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>124</v>
@@ -2570,7 +2564,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>125</v>
@@ -2579,7 +2573,7 @@
         <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>126</v>
@@ -2593,7 +2587,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>127</v>
@@ -2602,7 +2596,7 @@
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>128</v>
@@ -2616,7 +2610,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>129</v>
@@ -2625,7 +2619,7 @@
         <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>130</v>
@@ -2639,7 +2633,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>131</v>
@@ -2648,7 +2642,7 @@
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>132</v>
@@ -2662,7 +2656,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>133</v>
@@ -2671,7 +2665,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>134</v>
@@ -2685,7 +2679,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>135</v>
@@ -2694,7 +2688,7 @@
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>136</v>
@@ -2708,16 +2702,16 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>138</v>
@@ -2731,7 +2725,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>139</v>
@@ -2740,7 +2734,7 @@
         <v>52</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>140</v>
@@ -2754,7 +2748,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>141</v>
@@ -2763,7 +2757,7 @@
         <v>52</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>142</v>
@@ -2777,22 +2771,22 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>10</v>
+        <v>145</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>55</v>
@@ -2800,22 +2794,22 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>94</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>55</v>
@@ -2823,16 +2817,16 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>96</v>
@@ -2846,16 +2840,16 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>98</v>
@@ -2869,7 +2863,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>99</v>
@@ -2878,7 +2872,7 @@
         <v>52</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>100</v>
@@ -2892,7 +2886,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>101</v>
@@ -2901,7 +2895,7 @@
         <v>52</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>102</v>
@@ -2915,7 +2909,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>103</v>
@@ -2924,7 +2918,7 @@
         <v>52</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>104</v>
@@ -2938,16 +2932,16 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>106</v>
@@ -2961,7 +2955,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>107</v>
@@ -2970,7 +2964,7 @@
         <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>108</v>
@@ -2984,7 +2978,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>109</v>
@@ -2993,7 +2987,7 @@
         <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>110</v>
@@ -3007,7 +3001,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>111</v>
@@ -3016,7 +3010,7 @@
         <v>9</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>112</v>
@@ -3030,7 +3024,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>113</v>
@@ -3039,7 +3033,7 @@
         <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>114</v>
@@ -3053,16 +3047,16 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>116</v>
@@ -3076,7 +3070,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>117</v>
@@ -3085,7 +3079,7 @@
         <v>52</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>118</v>
@@ -3099,16 +3093,16 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>120</v>
@@ -3122,7 +3116,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>121</v>
@@ -3131,7 +3125,7 @@
         <v>9</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>122</v>
@@ -3145,7 +3139,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>123</v>
@@ -3154,7 +3148,7 @@
         <v>9</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>124</v>
@@ -3168,7 +3162,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>125</v>
@@ -3177,7 +3171,7 @@
         <v>9</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>126</v>
@@ -3191,7 +3185,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>127</v>
@@ -3200,7 +3194,7 @@
         <v>9</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>128</v>
@@ -3214,7 +3208,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>129</v>
@@ -3223,7 +3217,7 @@
         <v>9</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>130</v>
@@ -3237,7 +3231,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>131</v>
@@ -3246,7 +3240,7 @@
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>132</v>
@@ -3260,7 +3254,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>133</v>
@@ -3269,7 +3263,7 @@
         <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>134</v>
@@ -3283,7 +3277,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>135</v>
@@ -3292,7 +3286,7 @@
         <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>136</v>
@@ -3306,16 +3300,16 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>138</v>
@@ -3329,7 +3323,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>139</v>
@@ -3338,7 +3332,7 @@
         <v>52</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>140</v>
@@ -3352,7 +3346,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>141</v>
@@ -3361,7 +3355,7 @@
         <v>52</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>142</v>
@@ -3375,19 +3369,19 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -3398,7 +3392,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>148</v>
@@ -3407,7 +3401,7 @@
         <v>9</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>149</v>
@@ -3421,7 +3415,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>150</v>
@@ -3430,7 +3424,7 @@
         <v>9</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>151</v>
@@ -3444,7 +3438,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>152</v>
@@ -3453,7 +3447,7 @@
         <v>9</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>153</v>
@@ -3467,22 +3461,22 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>55</v>
@@ -3490,22 +3484,22 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>94</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>147</v>
+        <v>10</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>55</v>
@@ -3513,16 +3507,16 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>96</v>
@@ -3536,16 +3530,16 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>98</v>
@@ -3559,7 +3553,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>99</v>
@@ -3568,7 +3562,7 @@
         <v>52</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>100</v>
@@ -3582,7 +3576,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>101</v>
@@ -3591,7 +3585,7 @@
         <v>52</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>102</v>
@@ -3605,7 +3599,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>103</v>
@@ -3614,7 +3608,7 @@
         <v>52</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>104</v>
@@ -3628,16 +3622,16 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>106</v>
@@ -3651,7 +3645,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>107</v>
@@ -3660,7 +3654,7 @@
         <v>9</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>108</v>
@@ -3674,7 +3668,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>109</v>
@@ -3683,7 +3677,7 @@
         <v>9</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>110</v>
@@ -3697,7 +3691,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>111</v>
@@ -3706,7 +3700,7 @@
         <v>9</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>112</v>
@@ -3720,7 +3714,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>113</v>
@@ -3729,7 +3723,7 @@
         <v>9</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>114</v>
@@ -3743,16 +3737,16 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>116</v>
@@ -3766,7 +3760,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>117</v>
@@ -3775,7 +3769,7 @@
         <v>52</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>118</v>
@@ -3789,16 +3783,16 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>120</v>
@@ -3812,7 +3806,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>121</v>
@@ -3821,7 +3815,7 @@
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>122</v>
@@ -3835,7 +3829,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>123</v>
@@ -3844,7 +3838,7 @@
         <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>124</v>
@@ -3858,7 +3852,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>125</v>
@@ -3867,7 +3861,7 @@
         <v>9</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>126</v>
@@ -3881,7 +3875,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>127</v>
@@ -3890,7 +3884,7 @@
         <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>128</v>
@@ -3904,7 +3898,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>129</v>
@@ -3913,7 +3907,7 @@
         <v>9</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>130</v>
@@ -3927,7 +3921,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>131</v>
@@ -3936,7 +3930,7 @@
         <v>9</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>132</v>
@@ -3950,7 +3944,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>133</v>
@@ -3959,7 +3953,7 @@
         <v>9</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>134</v>
@@ -3973,7 +3967,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>135</v>
@@ -3982,7 +3976,7 @@
         <v>9</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>136</v>
@@ -3996,16 +3990,16 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>138</v>
@@ -4019,7 +4013,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>139</v>
@@ -4028,7 +4022,7 @@
         <v>52</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>140</v>
@@ -4042,7 +4036,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>141</v>
@@ -4051,7 +4045,7 @@
         <v>52</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>142</v>
@@ -4065,19 +4059,19 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>10</v>
@@ -4088,7 +4082,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>148</v>
@@ -4097,7 +4091,7 @@
         <v>9</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>149</v>
@@ -4111,7 +4105,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>150</v>
@@ -4120,7 +4114,7 @@
         <v>9</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>151</v>
@@ -4134,7 +4128,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>152</v>
@@ -4143,7 +4137,7 @@
         <v>9</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>153</v>
@@ -4160,39 +4154,39 @@
         <v>156</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>10</v>
@@ -4203,16 +4197,16 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>163</v>
@@ -4226,19 +4220,19 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>165</v>
+        <v>67</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>10</v>
@@ -4249,19 +4243,19 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>10</v>
@@ -4272,19 +4266,19 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>166</v>
+        <v>71</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>10</v>
@@ -4295,19 +4289,19 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>10</v>
@@ -4318,16 +4312,16 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>167</v>
@@ -4341,7 +4335,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>168</v>
@@ -4350,7 +4344,7 @@
         <v>9</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>169</v>
@@ -4364,7 +4358,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>170</v>
@@ -4373,7 +4367,7 @@
         <v>9</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>171</v>
@@ -4387,7 +4381,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>172</v>
@@ -4396,7 +4390,7 @@
         <v>9</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>173</v>
@@ -4410,39 +4404,39 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>163</v>
@@ -4451,113 +4445,113 @@
         <v>10</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D150" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G151" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D151" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G152" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F152" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G153" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>167</v>
@@ -4566,12 +4560,12 @@
         <v>10</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>168</v>
@@ -4580,7 +4574,7 @@
         <v>9</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>169</v>
@@ -4589,12 +4583,12 @@
         <v>10</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>170</v>
@@ -4603,7 +4597,7 @@
         <v>9</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>171</v>
@@ -4612,12 +4606,12 @@
         <v>10</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>172</v>
@@ -4626,7 +4620,7 @@
         <v>9</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>173</v>
@@ -4635,44 +4629,44 @@
         <v>10</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>178</v>
+        <v>55</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D159" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>183</v>
@@ -4686,7 +4680,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>184</v>
@@ -4695,7 +4689,7 @@
         <v>9</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>185</v>
@@ -4709,7 +4703,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>186</v>
@@ -4718,7 +4712,7 @@
         <v>9</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>187</v>
@@ -4732,7 +4726,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>188</v>
@@ -4741,7 +4735,7 @@
         <v>9</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>189</v>
@@ -4755,7 +4749,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>190</v>
@@ -4764,7 +4758,7 @@
         <v>9</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>191</v>
@@ -4778,7 +4772,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>192</v>
@@ -4787,10 +4781,10 @@
         <v>9</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="F164" s="2" t="s">
         <v>10</v>
@@ -4801,19 +4795,19 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="E165" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="F165" s="2" t="s">
         <v>10</v>
@@ -4824,7 +4818,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>195</v>
@@ -4833,10 +4827,10 @@
         <v>9</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>10</v>
@@ -4847,19 +4841,19 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="E167" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>10</v>
@@ -4870,7 +4864,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>198</v>
@@ -4879,7 +4873,7 @@
         <v>9</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>199</v>
@@ -4893,7 +4887,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>200</v>
@@ -4902,7 +4896,7 @@
         <v>9</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>201</v>
@@ -4916,7 +4910,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>202</v>
@@ -4925,7 +4919,7 @@
         <v>9</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>203</v>
@@ -4939,53 +4933,53 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>55</v>
+        <v>208</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D172" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B172" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D172" s="2" t="s">
+      <c r="E172" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G172" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="E172" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F172" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G172" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B173" s="2" t="s">
         <v>211</v>
@@ -4994,7 +4988,7 @@
         <v>52</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>212</v>
@@ -5003,12 +4997,12 @@
         <v>10</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>213</v>
@@ -5017,7 +5011,7 @@
         <v>52</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>214</v>
@@ -5026,12 +5020,12 @@
         <v>10</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>215</v>
@@ -5040,7 +5034,7 @@
         <v>52</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>216</v>
@@ -5049,12 +5043,12 @@
         <v>10</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B176" s="2" t="s">
         <v>217</v>
@@ -5063,7 +5057,7 @@
         <v>52</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>218</v>
@@ -5072,12 +5066,12 @@
         <v>10</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>219</v>
@@ -5086,7 +5080,7 @@
         <v>52</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>220</v>
@@ -5095,44 +5089,44 @@
         <v>10</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>221</v>
+        <v>179</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>222</v>
+        <v>181</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>210</v>
+        <v>55</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>183</v>
@@ -5146,7 +5140,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>184</v>
@@ -5155,7 +5149,7 @@
         <v>9</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>185</v>
@@ -5169,7 +5163,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>186</v>
@@ -5178,7 +5172,7 @@
         <v>9</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>187</v>
@@ -5192,7 +5186,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>188</v>
@@ -5201,7 +5195,7 @@
         <v>9</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>189</v>
@@ -5215,7 +5209,7 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>190</v>
@@ -5224,7 +5218,7 @@
         <v>9</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>191</v>
@@ -5238,7 +5232,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>192</v>
@@ -5247,10 +5241,10 @@
         <v>9</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>193</v>
+        <v>54</v>
       </c>
       <c r="F184" s="2" t="s">
         <v>10</v>
@@ -5261,19 +5255,19 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="F185" s="2" t="s">
         <v>10</v>
@@ -5284,7 +5278,7 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>195</v>
@@ -5293,10 +5287,10 @@
         <v>9</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c r="F186" s="2" t="s">
         <v>10</v>
@@ -5307,19 +5301,19 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F187" s="2" t="s">
         <v>10</v>
@@ -5330,7 +5324,7 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>198</v>
@@ -5339,7 +5333,7 @@
         <v>9</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>199</v>
@@ -5353,7 +5347,7 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>200</v>
@@ -5362,7 +5356,7 @@
         <v>9</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>201</v>
@@ -5376,7 +5370,7 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>202</v>
@@ -5385,7 +5379,7 @@
         <v>9</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>203</v>
@@ -5402,50 +5396,50 @@
         <v>223</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>224</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>55</v>
+        <v>225</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G192" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F192" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G192" s="2" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>211</v>
@@ -5454,7 +5448,7 @@
         <v>52</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>212</v>
@@ -5463,12 +5457,12 @@
         <v>10</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>213</v>
@@ -5477,7 +5471,7 @@
         <v>52</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>214</v>
@@ -5486,12 +5480,12 @@
         <v>10</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>215</v>
@@ -5500,7 +5494,7 @@
         <v>52</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>216</v>
@@ -5509,12 +5503,12 @@
         <v>10</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>217</v>
@@ -5523,7 +5517,7 @@
         <v>52</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>218</v>
@@ -5532,12 +5526,12 @@
         <v>10</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>219</v>
@@ -5546,7 +5540,7 @@
         <v>52</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>220</v>
@@ -5555,58 +5549,58 @@
         <v>10</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G199" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G199" s="2" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>211</v>
@@ -5615,7 +5609,7 @@
         <v>52</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>212</v>
@@ -5624,12 +5618,12 @@
         <v>10</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>213</v>
@@ -5638,7 +5632,7 @@
         <v>52</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>214</v>
@@ -5647,12 +5641,12 @@
         <v>10</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>215</v>
@@ -5661,7 +5655,7 @@
         <v>52</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>216</v>
@@ -5670,12 +5664,12 @@
         <v>10</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>217</v>
@@ -5684,7 +5678,7 @@
         <v>52</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>218</v>
@@ -5693,12 +5687,12 @@
         <v>10</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>219</v>
@@ -5707,7 +5701,7 @@
         <v>52</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>220</v>
@@ -5716,58 +5710,58 @@
         <v>10</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>34</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>211</v>
@@ -5776,7 +5770,7 @@
         <v>9</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>212</v>
@@ -5785,12 +5779,12 @@
         <v>34</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>213</v>
@@ -5799,21 +5793,21 @@
         <v>9</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>214</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>215</v>
@@ -5822,7 +5816,7 @@
         <v>9</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>216</v>
@@ -5831,12 +5825,12 @@
         <v>10</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>217</v>
@@ -5845,7 +5839,7 @@
         <v>9</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>218</v>
@@ -5854,12 +5848,12 @@
         <v>10</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>219</v>
@@ -5868,7 +5862,7 @@
         <v>9</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>220</v>
@@ -5877,58 +5871,58 @@
         <v>10</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G213" s="2" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>211</v>
@@ -5937,7 +5931,7 @@
         <v>52</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>212</v>
@@ -5946,12 +5940,12 @@
         <v>10</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>213</v>
@@ -5960,7 +5954,7 @@
         <v>52</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>214</v>
@@ -5969,12 +5963,12 @@
         <v>10</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>215</v>
@@ -5983,7 +5977,7 @@
         <v>52</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>216</v>
@@ -5992,12 +5986,12 @@
         <v>10</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>217</v>
@@ -6006,7 +6000,7 @@
         <v>52</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>218</v>
@@ -6015,12 +6009,12 @@
         <v>10</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>219</v>
@@ -6029,7 +6023,7 @@
         <v>52</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>220</v>
@@ -6038,58 +6032,58 @@
         <v>10</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G220" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>211</v>
@@ -6098,7 +6092,7 @@
         <v>52</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>212</v>
@@ -6107,12 +6101,12 @@
         <v>10</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>213</v>
@@ -6121,7 +6115,7 @@
         <v>52</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>214</v>
@@ -6130,12 +6124,12 @@
         <v>10</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>215</v>
@@ -6144,7 +6138,7 @@
         <v>52</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>216</v>
@@ -6153,12 +6147,12 @@
         <v>10</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>217</v>
@@ -6167,7 +6161,7 @@
         <v>52</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>218</v>
@@ -6176,12 +6170,12 @@
         <v>10</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>219</v>
@@ -6190,7 +6184,7 @@
         <v>52</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>220</v>
@@ -6199,81 +6193,81 @@
         <v>10</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B228" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G228" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G228" s="2" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>248</v>
@@ -6282,7 +6276,7 @@
         <v>9</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>249</v>
@@ -6291,12 +6285,12 @@
         <v>10</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>250</v>
@@ -6305,7 +6299,7 @@
         <v>9</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>251</v>
@@ -6314,44 +6308,44 @@
         <v>10</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>252</v>
+        <v>90</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>253</v>
+        <v>92</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>94</v>
@@ -6360,21 +6354,21 @@
         <v>10</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>96</v>
@@ -6383,21 +6377,21 @@
         <v>10</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>98</v>
@@ -6406,12 +6400,12 @@
         <v>10</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>99</v>
@@ -6420,7 +6414,7 @@
         <v>52</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>100</v>
@@ -6429,12 +6423,12 @@
         <v>10</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>101</v>
@@ -6443,7 +6437,7 @@
         <v>52</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>102</v>
@@ -6452,12 +6446,12 @@
         <v>10</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>103</v>
@@ -6466,7 +6460,7 @@
         <v>52</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>104</v>
@@ -6475,21 +6469,21 @@
         <v>10</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>106</v>
@@ -6498,12 +6492,12 @@
         <v>10</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>107</v>
@@ -6512,7 +6506,7 @@
         <v>9</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>108</v>
@@ -6521,12 +6515,12 @@
         <v>10</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>109</v>
@@ -6535,7 +6529,7 @@
         <v>9</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>110</v>
@@ -6544,12 +6538,12 @@
         <v>10</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>111</v>
@@ -6558,7 +6552,7 @@
         <v>9</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>112</v>
@@ -6567,12 +6561,12 @@
         <v>10</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>113</v>
@@ -6581,7 +6575,7 @@
         <v>9</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>114</v>
@@ -6590,21 +6584,21 @@
         <v>10</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>116</v>
@@ -6613,12 +6607,12 @@
         <v>10</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>117</v>
@@ -6627,7 +6621,7 @@
         <v>52</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>118</v>
@@ -6636,21 +6630,21 @@
         <v>10</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>120</v>
@@ -6659,12 +6653,12 @@
         <v>10</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>121</v>
@@ -6673,7 +6667,7 @@
         <v>9</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>122</v>
@@ -6682,12 +6676,12 @@
         <v>10</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>123</v>
@@ -6696,7 +6690,7 @@
         <v>9</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>124</v>
@@ -6705,12 +6699,12 @@
         <v>10</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>125</v>
@@ -6719,7 +6713,7 @@
         <v>9</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>126</v>
@@ -6728,12 +6722,12 @@
         <v>10</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>127</v>
@@ -6742,7 +6736,7 @@
         <v>9</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>128</v>
@@ -6751,12 +6745,12 @@
         <v>10</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>129</v>
@@ -6765,7 +6759,7 @@
         <v>9</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>130</v>
@@ -6774,12 +6768,12 @@
         <v>10</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>131</v>
@@ -6788,7 +6782,7 @@
         <v>9</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>132</v>
@@ -6797,12 +6791,12 @@
         <v>10</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>133</v>
@@ -6811,7 +6805,7 @@
         <v>9</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>134</v>
@@ -6820,12 +6814,12 @@
         <v>10</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>135</v>
@@ -6834,7 +6828,7 @@
         <v>9</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>136</v>
@@ -6843,21 +6837,21 @@
         <v>10</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>138</v>
@@ -6866,12 +6860,12 @@
         <v>10</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>139</v>
@@ -6880,7 +6874,7 @@
         <v>52</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>140</v>
@@ -6889,12 +6883,12 @@
         <v>10</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>141</v>
@@ -6903,7 +6897,7 @@
         <v>52</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>142</v>
@@ -6912,44 +6906,44 @@
         <v>10</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="F257" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>94</v>
@@ -6958,21 +6952,21 @@
         <v>10</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>96</v>
@@ -6981,21 +6975,21 @@
         <v>10</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>98</v>
@@ -7004,12 +6998,12 @@
         <v>10</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>99</v>
@@ -7018,7 +7012,7 @@
         <v>52</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>100</v>
@@ -7027,12 +7021,12 @@
         <v>10</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>101</v>
@@ -7041,7 +7035,7 @@
         <v>52</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>102</v>
@@ -7050,12 +7044,12 @@
         <v>10</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>103</v>
@@ -7064,7 +7058,7 @@
         <v>52</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>104</v>
@@ -7073,21 +7067,21 @@
         <v>10</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>106</v>
@@ -7096,12 +7090,12 @@
         <v>10</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>107</v>
@@ -7110,7 +7104,7 @@
         <v>9</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>108</v>
@@ -7119,12 +7113,12 @@
         <v>10</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>109</v>
@@ -7133,7 +7127,7 @@
         <v>9</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>110</v>
@@ -7142,12 +7136,12 @@
         <v>10</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>111</v>
@@ -7156,7 +7150,7 @@
         <v>9</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>112</v>
@@ -7165,12 +7159,12 @@
         <v>10</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>113</v>
@@ -7179,7 +7173,7 @@
         <v>9</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>114</v>
@@ -7188,21 +7182,21 @@
         <v>10</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>116</v>
@@ -7211,12 +7205,12 @@
         <v>10</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>117</v>
@@ -7225,7 +7219,7 @@
         <v>52</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>118</v>
@@ -7234,21 +7228,21 @@
         <v>10</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>120</v>
@@ -7257,12 +7251,12 @@
         <v>10</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>121</v>
@@ -7271,7 +7265,7 @@
         <v>9</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>122</v>
@@ -7280,12 +7274,12 @@
         <v>10</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>123</v>
@@ -7294,7 +7288,7 @@
         <v>9</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>124</v>
@@ -7303,12 +7297,12 @@
         <v>10</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>125</v>
@@ -7317,7 +7311,7 @@
         <v>9</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>126</v>
@@ -7326,12 +7320,12 @@
         <v>10</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>127</v>
@@ -7340,7 +7334,7 @@
         <v>9</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>128</v>
@@ -7349,12 +7343,12 @@
         <v>10</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>129</v>
@@ -7363,7 +7357,7 @@
         <v>9</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>130</v>
@@ -7372,12 +7366,12 @@
         <v>10</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>131</v>
@@ -7386,7 +7380,7 @@
         <v>9</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>132</v>
@@ -7395,12 +7389,12 @@
         <v>10</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>133</v>
@@ -7409,7 +7403,7 @@
         <v>9</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>134</v>
@@ -7418,12 +7412,12 @@
         <v>10</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>135</v>
@@ -7432,7 +7426,7 @@
         <v>9</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>136</v>
@@ -7441,21 +7435,21 @@
         <v>10</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>138</v>
@@ -7464,12 +7458,12 @@
         <v>10</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>139</v>
@@ -7478,7 +7472,7 @@
         <v>52</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>140</v>
@@ -7487,12 +7481,12 @@
         <v>10</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>141</v>
@@ -7501,7 +7495,7 @@
         <v>52</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>142</v>
@@ -7510,44 +7504,44 @@
         <v>10</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="F283" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>94</v>
@@ -7556,21 +7550,21 @@
         <v>10</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>96</v>
@@ -7579,21 +7573,21 @@
         <v>10</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>98</v>
@@ -7602,12 +7596,12 @@
         <v>10</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>99</v>
@@ -7616,7 +7610,7 @@
         <v>52</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>100</v>
@@ -7625,12 +7619,12 @@
         <v>10</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>101</v>
@@ -7639,7 +7633,7 @@
         <v>52</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>102</v>
@@ -7648,12 +7642,12 @@
         <v>10</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>103</v>
@@ -7662,7 +7656,7 @@
         <v>52</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>104</v>
@@ -7671,21 +7665,21 @@
         <v>10</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>106</v>
@@ -7694,12 +7688,12 @@
         <v>10</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>107</v>
@@ -7708,7 +7702,7 @@
         <v>9</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>108</v>
@@ -7717,12 +7711,12 @@
         <v>10</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>109</v>
@@ -7731,7 +7725,7 @@
         <v>9</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>110</v>
@@ -7740,12 +7734,12 @@
         <v>10</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>111</v>
@@ -7754,7 +7748,7 @@
         <v>9</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>112</v>
@@ -7763,12 +7757,12 @@
         <v>10</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>113</v>
@@ -7777,7 +7771,7 @@
         <v>9</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>114</v>
@@ -7786,21 +7780,21 @@
         <v>10</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>116</v>
@@ -7809,12 +7803,12 @@
         <v>10</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>117</v>
@@ -7823,7 +7817,7 @@
         <v>52</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>118</v>
@@ -7832,21 +7826,21 @@
         <v>10</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>120</v>
@@ -7855,12 +7849,12 @@
         <v>10</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>121</v>
@@ -7869,7 +7863,7 @@
         <v>9</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>122</v>
@@ -7878,12 +7872,12 @@
         <v>10</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>123</v>
@@ -7892,7 +7886,7 @@
         <v>9</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>124</v>
@@ -7901,12 +7895,12 @@
         <v>10</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>125</v>
@@ -7915,7 +7909,7 @@
         <v>9</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>126</v>
@@ -7924,12 +7918,12 @@
         <v>10</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>127</v>
@@ -7938,7 +7932,7 @@
         <v>9</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>128</v>
@@ -7947,12 +7941,12 @@
         <v>10</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>129</v>
@@ -7961,7 +7955,7 @@
         <v>9</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>130</v>
@@ -7970,12 +7964,12 @@
         <v>10</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>131</v>
@@ -7984,7 +7978,7 @@
         <v>9</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>132</v>
@@ -7993,12 +7987,12 @@
         <v>10</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>133</v>
@@ -8007,7 +8001,7 @@
         <v>9</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>134</v>
@@ -8016,12 +8010,12 @@
         <v>10</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>135</v>
@@ -8030,7 +8024,7 @@
         <v>9</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>136</v>
@@ -8039,21 +8033,21 @@
         <v>10</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>138</v>
@@ -8062,12 +8056,12 @@
         <v>10</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>139</v>
@@ -8076,7 +8070,7 @@
         <v>52</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>140</v>
@@ -8085,12 +8079,12 @@
         <v>10</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>141</v>
@@ -8099,7 +8093,7 @@
         <v>52</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>142</v>
@@ -8108,44 +8102,44 @@
         <v>10</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>94</v>
@@ -8154,21 +8148,21 @@
         <v>10</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>96</v>
@@ -8177,21 +8171,21 @@
         <v>10</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>98</v>
@@ -8200,12 +8194,12 @@
         <v>10</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>99</v>
@@ -8214,7 +8208,7 @@
         <v>52</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>100</v>
@@ -8223,12 +8217,12 @@
         <v>10</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>101</v>
@@ -8237,7 +8231,7 @@
         <v>52</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>102</v>
@@ -8246,12 +8240,12 @@
         <v>10</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>103</v>
@@ -8260,7 +8254,7 @@
         <v>52</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>104</v>
@@ -8269,21 +8263,21 @@
         <v>10</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>106</v>
@@ -8292,12 +8286,12 @@
         <v>10</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>107</v>
@@ -8306,7 +8300,7 @@
         <v>9</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>108</v>
@@ -8315,12 +8309,12 @@
         <v>10</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>109</v>
@@ -8329,7 +8323,7 @@
         <v>9</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>110</v>
@@ -8338,12 +8332,12 @@
         <v>10</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>111</v>
@@ -8352,7 +8346,7 @@
         <v>9</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>112</v>
@@ -8361,12 +8355,12 @@
         <v>10</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>113</v>
@@ -8375,7 +8369,7 @@
         <v>9</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>114</v>
@@ -8384,21 +8378,21 @@
         <v>10</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>116</v>
@@ -8407,12 +8401,12 @@
         <v>10</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>117</v>
@@ -8421,7 +8415,7 @@
         <v>52</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>118</v>
@@ -8430,21 +8424,21 @@
         <v>10</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>120</v>
@@ -8453,12 +8447,12 @@
         <v>10</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>121</v>
@@ -8467,7 +8461,7 @@
         <v>9</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>122</v>
@@ -8476,12 +8470,12 @@
         <v>10</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>123</v>
@@ -8490,7 +8484,7 @@
         <v>9</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>124</v>
@@ -8499,12 +8493,12 @@
         <v>10</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>125</v>
@@ -8513,7 +8507,7 @@
         <v>9</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>126</v>
@@ -8522,12 +8516,12 @@
         <v>10</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>127</v>
@@ -8536,7 +8530,7 @@
         <v>9</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>128</v>
@@ -8545,12 +8539,12 @@
         <v>10</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>129</v>
@@ -8559,7 +8553,7 @@
         <v>9</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>130</v>
@@ -8568,12 +8562,12 @@
         <v>10</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>131</v>
@@ -8582,7 +8576,7 @@
         <v>9</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>132</v>
@@ -8591,12 +8585,12 @@
         <v>10</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>133</v>
@@ -8605,7 +8599,7 @@
         <v>9</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>134</v>
@@ -8614,12 +8608,12 @@
         <v>10</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>135</v>
@@ -8628,7 +8622,7 @@
         <v>9</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>136</v>
@@ -8637,21 +8631,21 @@
         <v>10</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>138</v>
@@ -8660,12 +8654,12 @@
         <v>10</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>139</v>
@@ -8674,7 +8668,7 @@
         <v>52</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>140</v>
@@ -8683,12 +8677,12 @@
         <v>10</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>141</v>
@@ -8697,7 +8691,7 @@
         <v>52</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>142</v>
@@ -8706,44 +8700,44 @@
         <v>10</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="F335" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G335" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>94</v>
@@ -8752,21 +8746,21 @@
         <v>10</v>
       </c>
       <c r="G336" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>96</v>
@@ -8775,21 +8769,21 @@
         <v>10</v>
       </c>
       <c r="G337" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>98</v>
@@ -8798,12 +8792,12 @@
         <v>10</v>
       </c>
       <c r="G338" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>99</v>
@@ -8812,7 +8806,7 @@
         <v>52</v>
       </c>
       <c r="D339" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>100</v>
@@ -8821,12 +8815,12 @@
         <v>10</v>
       </c>
       <c r="G339" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>101</v>
@@ -8835,7 +8829,7 @@
         <v>52</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>102</v>
@@ -8844,12 +8838,12 @@
         <v>10</v>
       </c>
       <c r="G340" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>103</v>
@@ -8858,7 +8852,7 @@
         <v>52</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>104</v>
@@ -8867,21 +8861,21 @@
         <v>10</v>
       </c>
       <c r="G341" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>106</v>
@@ -8890,12 +8884,12 @@
         <v>10</v>
       </c>
       <c r="G342" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>107</v>
@@ -8904,7 +8898,7 @@
         <v>9</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>108</v>
@@ -8913,12 +8907,12 @@
         <v>10</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>109</v>
@@ -8927,7 +8921,7 @@
         <v>9</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>110</v>
@@ -8936,12 +8930,12 @@
         <v>10</v>
       </c>
       <c r="G344" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>111</v>
@@ -8950,7 +8944,7 @@
         <v>9</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>112</v>
@@ -8959,12 +8953,12 @@
         <v>10</v>
       </c>
       <c r="G345" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B346" s="2" t="s">
         <v>113</v>
@@ -8973,7 +8967,7 @@
         <v>9</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>114</v>
@@ -8982,21 +8976,21 @@
         <v>10</v>
       </c>
       <c r="G346" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B347" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>116</v>
@@ -9005,12 +8999,12 @@
         <v>10</v>
       </c>
       <c r="G347" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B348" s="2" t="s">
         <v>117</v>
@@ -9019,7 +9013,7 @@
         <v>52</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>118</v>
@@ -9028,21 +9022,21 @@
         <v>10</v>
       </c>
       <c r="G348" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B349" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>120</v>
@@ -9051,12 +9045,12 @@
         <v>10</v>
       </c>
       <c r="G349" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>121</v>
@@ -9065,7 +9059,7 @@
         <v>9</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>122</v>
@@ -9074,12 +9068,12 @@
         <v>10</v>
       </c>
       <c r="G350" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B351" s="2" t="s">
         <v>123</v>
@@ -9088,7 +9082,7 @@
         <v>9</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>124</v>
@@ -9097,12 +9091,12 @@
         <v>10</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>125</v>
@@ -9111,7 +9105,7 @@
         <v>9</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>126</v>
@@ -9120,12 +9114,12 @@
         <v>10</v>
       </c>
       <c r="G352" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B353" s="2" t="s">
         <v>127</v>
@@ -9134,7 +9128,7 @@
         <v>9</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>128</v>
@@ -9143,12 +9137,12 @@
         <v>10</v>
       </c>
       <c r="G353" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>129</v>
@@ -9157,7 +9151,7 @@
         <v>9</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>130</v>
@@ -9166,12 +9160,12 @@
         <v>10</v>
       </c>
       <c r="G354" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>131</v>
@@ -9180,7 +9174,7 @@
         <v>9</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>132</v>
@@ -9189,12 +9183,12 @@
         <v>10</v>
       </c>
       <c r="G355" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>133</v>
@@ -9203,7 +9197,7 @@
         <v>9</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>134</v>
@@ -9212,12 +9206,12 @@
         <v>10</v>
       </c>
       <c r="G356" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>135</v>
@@ -9226,7 +9220,7 @@
         <v>9</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>136</v>
@@ -9235,21 +9229,21 @@
         <v>10</v>
       </c>
       <c r="G357" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>138</v>
@@ -9258,12 +9252,12 @@
         <v>10</v>
       </c>
       <c r="G358" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>139</v>
@@ -9272,7 +9266,7 @@
         <v>52</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>140</v>
@@ -9281,12 +9275,12 @@
         <v>10</v>
       </c>
       <c r="G359" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>141</v>
@@ -9295,7 +9289,7 @@
         <v>52</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>142</v>
@@ -9304,24 +9298,24 @@
         <v>10</v>
       </c>
       <c r="G360" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="F361" s="2" t="s">
         <v>10</v>
@@ -9332,16 +9326,16 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>94</v>
@@ -9350,21 +9344,21 @@
         <v>10</v>
       </c>
       <c r="G362" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>96</v>
@@ -9373,21 +9367,21 @@
         <v>10</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>98</v>
@@ -9396,12 +9390,12 @@
         <v>10</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>99</v>
@@ -9410,7 +9404,7 @@
         <v>52</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>100</v>
@@ -9419,12 +9413,12 @@
         <v>10</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>101</v>
@@ -9433,7 +9427,7 @@
         <v>52</v>
       </c>
       <c r="D366" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>102</v>
@@ -9442,12 +9436,12 @@
         <v>10</v>
       </c>
       <c r="G366" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>103</v>
@@ -9456,7 +9450,7 @@
         <v>52</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>104</v>
@@ -9465,21 +9459,21 @@
         <v>10</v>
       </c>
       <c r="G367" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>106</v>
@@ -9488,12 +9482,12 @@
         <v>10</v>
       </c>
       <c r="G368" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>107</v>
@@ -9502,7 +9496,7 @@
         <v>9</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>108</v>
@@ -9511,12 +9505,12 @@
         <v>10</v>
       </c>
       <c r="G369" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>109</v>
@@ -9525,7 +9519,7 @@
         <v>9</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>110</v>
@@ -9534,12 +9528,12 @@
         <v>10</v>
       </c>
       <c r="G370" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>111</v>
@@ -9548,7 +9542,7 @@
         <v>9</v>
       </c>
       <c r="D371" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E371" s="2" t="s">
         <v>112</v>
@@ -9557,12 +9551,12 @@
         <v>10</v>
       </c>
       <c r="G371" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>113</v>
@@ -9571,7 +9565,7 @@
         <v>9</v>
       </c>
       <c r="D372" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E372" s="2" t="s">
         <v>114</v>
@@ -9580,21 +9574,21 @@
         <v>10</v>
       </c>
       <c r="G372" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>116</v>
@@ -9603,12 +9597,12 @@
         <v>10</v>
       </c>
       <c r="G373" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>117</v>
@@ -9617,7 +9611,7 @@
         <v>52</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>118</v>
@@ -9626,21 +9620,21 @@
         <v>10</v>
       </c>
       <c r="G374" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D375" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E375" s="2" t="s">
         <v>120</v>
@@ -9649,12 +9643,12 @@
         <v>10</v>
       </c>
       <c r="G375" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>121</v>
@@ -9663,7 +9657,7 @@
         <v>9</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E376" s="2" t="s">
         <v>122</v>
@@ -9672,12 +9666,12 @@
         <v>10</v>
       </c>
       <c r="G376" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>123</v>
@@ -9686,7 +9680,7 @@
         <v>9</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E377" s="2" t="s">
         <v>124</v>
@@ -9695,12 +9689,12 @@
         <v>10</v>
       </c>
       <c r="G377" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>125</v>
@@ -9709,7 +9703,7 @@
         <v>9</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E378" s="2" t="s">
         <v>126</v>
@@ -9718,12 +9712,12 @@
         <v>10</v>
       </c>
       <c r="G378" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>127</v>
@@ -9732,7 +9726,7 @@
         <v>9</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E379" s="2" t="s">
         <v>128</v>
@@ -9741,12 +9735,12 @@
         <v>10</v>
       </c>
       <c r="G379" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>129</v>
@@ -9755,7 +9749,7 @@
         <v>9</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>130</v>
@@ -9764,12 +9758,12 @@
         <v>10</v>
       </c>
       <c r="G380" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>131</v>
@@ -9778,7 +9772,7 @@
         <v>9</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>132</v>
@@ -9787,12 +9781,12 @@
         <v>10</v>
       </c>
       <c r="G381" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>133</v>
@@ -9801,7 +9795,7 @@
         <v>9</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>134</v>
@@ -9810,12 +9804,12 @@
         <v>10</v>
       </c>
       <c r="G382" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>135</v>
@@ -9824,7 +9818,7 @@
         <v>9</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E383" s="2" t="s">
         <v>136</v>
@@ -9833,21 +9827,21 @@
         <v>10</v>
       </c>
       <c r="G383" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D384" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E384" s="2" t="s">
         <v>138</v>
@@ -9856,12 +9850,12 @@
         <v>10</v>
       </c>
       <c r="G384" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>139</v>
@@ -9870,7 +9864,7 @@
         <v>52</v>
       </c>
       <c r="D385" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E385" s="2" t="s">
         <v>140</v>
@@ -9879,12 +9873,12 @@
         <v>10</v>
       </c>
       <c r="G385" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>141</v>
@@ -9893,7 +9887,7 @@
         <v>52</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E386" s="2" t="s">
         <v>142</v>
@@ -9902,7 +9896,7 @@
         <v>10</v>
       </c>
       <c r="G386" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="387">
@@ -9910,50 +9904,50 @@
         <v>269</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D387" s="2" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
       <c r="F387" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G387" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E388" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F388" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G388" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="B388" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C388" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D388" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E388" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F388" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G388" s="2" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>211</v>
@@ -9962,7 +9956,7 @@
         <v>52</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E389" s="2" t="s">
         <v>212</v>
@@ -9971,12 +9965,12 @@
         <v>10</v>
       </c>
       <c r="G389" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>213</v>
@@ -9985,7 +9979,7 @@
         <v>52</v>
       </c>
       <c r="D390" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E390" s="2" t="s">
         <v>214</v>
@@ -9994,12 +9988,12 @@
         <v>10</v>
       </c>
       <c r="G390" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>215</v>
@@ -10008,7 +10002,7 @@
         <v>52</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E391" s="2" t="s">
         <v>216</v>
@@ -10017,12 +10011,12 @@
         <v>10</v>
       </c>
       <c r="G391" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>217</v>
@@ -10031,7 +10025,7 @@
         <v>52</v>
       </c>
       <c r="D392" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E392" s="2" t="s">
         <v>218</v>
@@ -10040,12 +10034,12 @@
         <v>10</v>
       </c>
       <c r="G392" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>219</v>
@@ -10054,7 +10048,7 @@
         <v>52</v>
       </c>
       <c r="D393" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E393" s="2" t="s">
         <v>220</v>
@@ -10063,44 +10057,44 @@
         <v>10</v>
       </c>
       <c r="G393" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>221</v>
+        <v>90</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>222</v>
+        <v>92</v>
       </c>
       <c r="F394" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G394" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D395" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>94</v>
@@ -10109,21 +10103,21 @@
         <v>10</v>
       </c>
       <c r="G395" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E396" s="2" t="s">
         <v>96</v>
@@ -10132,21 +10126,21 @@
         <v>10</v>
       </c>
       <c r="G396" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>98</v>
@@ -10155,12 +10149,12 @@
         <v>10</v>
       </c>
       <c r="G397" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>99</v>
@@ -10169,7 +10163,7 @@
         <v>52</v>
       </c>
       <c r="D398" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>100</v>
@@ -10178,12 +10172,12 @@
         <v>10</v>
       </c>
       <c r="G398" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>101</v>
@@ -10192,7 +10186,7 @@
         <v>52</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E399" s="2" t="s">
         <v>102</v>
@@ -10201,12 +10195,12 @@
         <v>10</v>
       </c>
       <c r="G399" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>103</v>
@@ -10215,7 +10209,7 @@
         <v>52</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>104</v>
@@ -10224,21 +10218,21 @@
         <v>10</v>
       </c>
       <c r="G400" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>106</v>
@@ -10247,12 +10241,12 @@
         <v>10</v>
       </c>
       <c r="G401" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>107</v>
@@ -10261,7 +10255,7 @@
         <v>9</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>108</v>
@@ -10270,12 +10264,12 @@
         <v>10</v>
       </c>
       <c r="G402" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>109</v>
@@ -10284,7 +10278,7 @@
         <v>9</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>110</v>
@@ -10293,12 +10287,12 @@
         <v>10</v>
       </c>
       <c r="G403" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>111</v>
@@ -10307,7 +10301,7 @@
         <v>9</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E404" s="2" t="s">
         <v>112</v>
@@ -10316,12 +10310,12 @@
         <v>10</v>
       </c>
       <c r="G404" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>113</v>
@@ -10330,7 +10324,7 @@
         <v>9</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>114</v>
@@ -10339,21 +10333,21 @@
         <v>10</v>
       </c>
       <c r="G405" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E406" s="2" t="s">
         <v>116</v>
@@ -10362,12 +10356,12 @@
         <v>10</v>
       </c>
       <c r="G406" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>117</v>
@@ -10376,7 +10370,7 @@
         <v>52</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E407" s="2" t="s">
         <v>118</v>
@@ -10385,21 +10379,21 @@
         <v>10</v>
       </c>
       <c r="G407" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>120</v>
@@ -10408,12 +10402,12 @@
         <v>10</v>
       </c>
       <c r="G408" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>121</v>
@@ -10422,7 +10416,7 @@
         <v>9</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E409" s="2" t="s">
         <v>122</v>
@@ -10431,12 +10425,12 @@
         <v>10</v>
       </c>
       <c r="G409" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>123</v>
@@ -10445,7 +10439,7 @@
         <v>9</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E410" s="2" t="s">
         <v>124</v>
@@ -10454,12 +10448,12 @@
         <v>10</v>
       </c>
       <c r="G410" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>125</v>
@@ -10468,7 +10462,7 @@
         <v>9</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E411" s="2" t="s">
         <v>126</v>
@@ -10477,12 +10471,12 @@
         <v>10</v>
       </c>
       <c r="G411" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>127</v>
@@ -10491,7 +10485,7 @@
         <v>9</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>128</v>
@@ -10500,12 +10494,12 @@
         <v>10</v>
       </c>
       <c r="G412" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>129</v>
@@ -10514,7 +10508,7 @@
         <v>9</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>130</v>
@@ -10523,12 +10517,12 @@
         <v>10</v>
       </c>
       <c r="G413" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>131</v>
@@ -10537,7 +10531,7 @@
         <v>9</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E414" s="2" t="s">
         <v>132</v>
@@ -10546,12 +10540,12 @@
         <v>10</v>
       </c>
       <c r="G414" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>133</v>
@@ -10560,7 +10554,7 @@
         <v>9</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E415" s="2" t="s">
         <v>134</v>
@@ -10569,12 +10563,12 @@
         <v>10</v>
       </c>
       <c r="G415" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>135</v>
@@ -10583,7 +10577,7 @@
         <v>9</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>136</v>
@@ -10592,21 +10586,21 @@
         <v>10</v>
       </c>
       <c r="G416" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E417" s="2" t="s">
         <v>138</v>
@@ -10615,12 +10609,12 @@
         <v>10</v>
       </c>
       <c r="G417" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>139</v>
@@ -10629,7 +10623,7 @@
         <v>52</v>
       </c>
       <c r="D418" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E418" s="2" t="s">
         <v>140</v>
@@ -10638,12 +10632,12 @@
         <v>10</v>
       </c>
       <c r="G418" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>141</v>
@@ -10652,7 +10646,7 @@
         <v>52</v>
       </c>
       <c r="D419" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>142</v>
@@ -10661,24 +10655,24 @@
         <v>10</v>
       </c>
       <c r="G419" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="F420" s="2" t="s">
         <v>10</v>
@@ -10689,16 +10683,16 @@
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D421" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E421" s="2" t="s">
         <v>94</v>
@@ -10707,21 +10701,21 @@
         <v>10</v>
       </c>
       <c r="G421" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D422" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E422" s="2" t="s">
         <v>96</v>
@@ -10730,21 +10724,21 @@
         <v>10</v>
       </c>
       <c r="G422" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D423" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>98</v>
@@ -10753,12 +10747,12 @@
         <v>10</v>
       </c>
       <c r="G423" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>99</v>
@@ -10767,7 +10761,7 @@
         <v>52</v>
       </c>
       <c r="D424" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E424" s="2" t="s">
         <v>100</v>
@@ -10776,12 +10770,12 @@
         <v>10</v>
       </c>
       <c r="G424" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>101</v>
@@ -10790,7 +10784,7 @@
         <v>52</v>
       </c>
       <c r="D425" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E425" s="2" t="s">
         <v>102</v>
@@ -10799,12 +10793,12 @@
         <v>10</v>
       </c>
       <c r="G425" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>103</v>
@@ -10813,7 +10807,7 @@
         <v>52</v>
       </c>
       <c r="D426" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>104</v>
@@ -10822,21 +10816,21 @@
         <v>10</v>
       </c>
       <c r="G426" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D427" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E427" s="2" t="s">
         <v>106</v>
@@ -10845,12 +10839,12 @@
         <v>10</v>
       </c>
       <c r="G427" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>107</v>
@@ -10859,7 +10853,7 @@
         <v>9</v>
       </c>
       <c r="D428" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E428" s="2" t="s">
         <v>108</v>
@@ -10868,12 +10862,12 @@
         <v>10</v>
       </c>
       <c r="G428" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>109</v>
@@ -10882,7 +10876,7 @@
         <v>9</v>
       </c>
       <c r="D429" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E429" s="2" t="s">
         <v>110</v>
@@ -10891,12 +10885,12 @@
         <v>10</v>
       </c>
       <c r="G429" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>111</v>
@@ -10905,7 +10899,7 @@
         <v>9</v>
       </c>
       <c r="D430" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E430" s="2" t="s">
         <v>112</v>
@@ -10914,12 +10908,12 @@
         <v>10</v>
       </c>
       <c r="G430" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>113</v>
@@ -10928,7 +10922,7 @@
         <v>9</v>
       </c>
       <c r="D431" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>114</v>
@@ -10937,21 +10931,21 @@
         <v>10</v>
       </c>
       <c r="G431" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D432" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>116</v>
@@ -10960,12 +10954,12 @@
         <v>10</v>
       </c>
       <c r="G432" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>117</v>
@@ -10974,7 +10968,7 @@
         <v>52</v>
       </c>
       <c r="D433" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E433" s="2" t="s">
         <v>118</v>
@@ -10983,21 +10977,21 @@
         <v>10</v>
       </c>
       <c r="G433" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D434" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>120</v>
@@ -11006,12 +11000,12 @@
         <v>10</v>
       </c>
       <c r="G434" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>121</v>
@@ -11020,7 +11014,7 @@
         <v>9</v>
       </c>
       <c r="D435" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>122</v>
@@ -11029,12 +11023,12 @@
         <v>10</v>
       </c>
       <c r="G435" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>123</v>
@@ -11043,7 +11037,7 @@
         <v>9</v>
       </c>
       <c r="D436" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>124</v>
@@ -11052,12 +11046,12 @@
         <v>10</v>
       </c>
       <c r="G436" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>125</v>
@@ -11066,7 +11060,7 @@
         <v>9</v>
       </c>
       <c r="D437" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>126</v>
@@ -11075,12 +11069,12 @@
         <v>10</v>
       </c>
       <c r="G437" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>127</v>
@@ -11089,7 +11083,7 @@
         <v>9</v>
       </c>
       <c r="D438" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>128</v>
@@ -11098,12 +11092,12 @@
         <v>10</v>
       </c>
       <c r="G438" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>129</v>
@@ -11112,7 +11106,7 @@
         <v>9</v>
       </c>
       <c r="D439" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>130</v>
@@ -11121,12 +11115,12 @@
         <v>10</v>
       </c>
       <c r="G439" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>131</v>
@@ -11135,7 +11129,7 @@
         <v>9</v>
       </c>
       <c r="D440" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>132</v>
@@ -11144,12 +11138,12 @@
         <v>10</v>
       </c>
       <c r="G440" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>133</v>
@@ -11158,7 +11152,7 @@
         <v>9</v>
       </c>
       <c r="D441" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>134</v>
@@ -11167,12 +11161,12 @@
         <v>10</v>
       </c>
       <c r="G441" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>135</v>
@@ -11181,7 +11175,7 @@
         <v>9</v>
       </c>
       <c r="D442" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E442" s="2" t="s">
         <v>136</v>
@@ -11190,21 +11184,21 @@
         <v>10</v>
       </c>
       <c r="G442" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="D443" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>138</v>
@@ -11213,12 +11207,12 @@
         <v>10</v>
       </c>
       <c r="G443" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>139</v>
@@ -11227,7 +11221,7 @@
         <v>52</v>
       </c>
       <c r="D444" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>140</v>
@@ -11236,12 +11230,12 @@
         <v>10</v>
       </c>
       <c r="G444" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>141</v>
@@ -11250,7 +11244,7 @@
         <v>52</v>
       </c>
       <c r="D445" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>142</v>
@@ -11259,7 +11253,7 @@
         <v>10</v>
       </c>
       <c r="G445" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="446">
@@ -11267,50 +11261,50 @@
         <v>277</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D446" s="2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>144</v>
+        <v>207</v>
       </c>
       <c r="F446" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G446" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B447" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C447" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D447" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E447" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F447" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G447" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="B447" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C447" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D447" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E447" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F447" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G447" s="2" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>211</v>
@@ -11319,7 +11313,7 @@
         <v>52</v>
       </c>
       <c r="D448" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>212</v>
@@ -11328,12 +11322,12 @@
         <v>10</v>
       </c>
       <c r="G448" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>213</v>
@@ -11342,7 +11336,7 @@
         <v>52</v>
       </c>
       <c r="D449" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>214</v>
@@ -11351,12 +11345,12 @@
         <v>10</v>
       </c>
       <c r="G449" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>215</v>
@@ -11365,7 +11359,7 @@
         <v>52</v>
       </c>
       <c r="D450" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>216</v>
@@ -11374,12 +11368,12 @@
         <v>10</v>
       </c>
       <c r="G450" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>217</v>
@@ -11388,7 +11382,7 @@
         <v>52</v>
       </c>
       <c r="D451" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>218</v>
@@ -11397,12 +11391,12 @@
         <v>10</v>
       </c>
       <c r="G451" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>219</v>
@@ -11411,7 +11405,7 @@
         <v>52</v>
       </c>
       <c r="D452" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>220</v>
@@ -11420,35 +11414,35 @@
         <v>10</v>
       </c>
       <c r="G452" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>221</v>
+        <v>281</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D453" s="2" t="s">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>222</v>
+        <v>282</v>
       </c>
       <c r="F453" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G453" s="2" t="s">
-        <v>281</v>
+        <v>55</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>283</v>
@@ -11471,7 +11465,7 @@
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>285</v>
@@ -11494,7 +11488,7 @@
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>287</v>
@@ -11517,7 +11511,7 @@
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>289</v>
@@ -11540,7 +11534,7 @@
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>291</v>
@@ -11563,7 +11557,7 @@
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>293</v>
@@ -11586,7 +11580,7 @@
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>295</v>
@@ -11595,7 +11589,7 @@
         <v>52</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>75</v>
+        <v>239</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>296</v>
@@ -11609,7 +11603,7 @@
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>297</v>
@@ -11618,7 +11612,7 @@
         <v>52</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E461" s="2" t="s">
         <v>298</v>
@@ -11632,16 +11626,16 @@
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>299</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="E462" s="2" t="s">
         <v>300</v>
@@ -11655,7 +11649,7 @@
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>301</v>
@@ -11678,19 +11672,19 @@
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>75</v>
+        <v>305</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F464" s="2" t="s">
         <v>10</v>
@@ -11701,16 +11695,16 @@
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B465" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C465" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D465" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="B465" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C465" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D465" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="E465" s="2" t="s">
         <v>308</v>
@@ -11724,7 +11718,7 @@
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>309</v>
@@ -11733,7 +11727,7 @@
         <v>9</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>310</v>
@@ -11747,7 +11741,7 @@
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>311</v>
@@ -11756,7 +11750,7 @@
         <v>9</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E467" s="2" t="s">
         <v>312</v>
@@ -11765,29 +11759,6 @@
         <v>10</v>
       </c>
       <c r="G467" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B468" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="C468" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D468" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E468" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F468" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G468" s="2" t="s">
         <v>55</v>
       </c>
     </row>

--- a/docs/Mapping_casi_uso/matrimoni/Matr_008.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_008.xlsx
@@ -125,7 +125,7 @@
     <t>59</t>
   </si>
   <si>
-    <t>62</t>
+    <t>62.1</t>
   </si>
   <si>
     <t>62-bis</t>
